--- a/fhir/ValueSet-ehealth-treatment-areas-xc.xlsx
+++ b/fhir/ValueSet-ehealth-treatment-areas-xc.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-ehealth-treatment-areas-xc.xlsx
+++ b/fhir/ValueSet-ehealth-treatment-areas-xc.xlsx
@@ -8,12 +8,14 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include ValueSet #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Include ValueSet #1" r:id="rId5" sheetId="3"/>
+    <sheet name="Include ValueSet #2" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -372,7 +374,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -389,13 +391,51 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
         <v>31</v>
       </c>
     </row>

--- a/fhir/ValueSet-ehealth-treatment-areas-xc.xlsx
+++ b/fhir/ValueSet-ehealth-treatment-areas-xc.xlsx
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-ehealth-treatment-areas-xc.xlsx
+++ b/fhir/ValueSet-ehealth-treatment-areas-xc.xlsx
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-ehealth-treatment-areas-xc.xlsx
+++ b/fhir/ValueSet-ehealth-treatment-areas-xc.xlsx
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-ehealth-treatment-areas-xc.xlsx
+++ b/fhir/ValueSet-ehealth-treatment-areas-xc.xlsx
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-ehealth-treatment-areas-xc.xlsx
+++ b/fhir/ValueSet-ehealth-treatment-areas-xc.xlsx
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
